--- a/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
+++ b/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2A39F6-5AF4-4E2F-BEA0-D60F70B350FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4780AB0-D514-48BF-B10B-41CFC43C0E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
   </bookViews>
   <sheets>
     <sheet name="Barbarossa" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="210">
   <si>
     <t>Scenario</t>
   </si>
@@ -4132,12 +4132,43 @@
 (Not on Standard)</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Murder Holes and Herbal Medicine automatically researched for Teutons</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>No Carvel Hull
+No Spies</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4360,6 +4391,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4369,7 +4413,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -4505,11 +4549,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4642,6 +4710,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5293,15 +5388,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8EBFBFB-BFC3-45F2-8AE9-505265B14120}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5315,7 +5416,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="9" t="s">
         <v>83</v>
       </c>
@@ -5329,7 +5435,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
@@ -5343,7 +5458,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>88</v>
       </c>
@@ -5357,7 +5481,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
       </c>
@@ -5371,7 +5498,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="12" t="s">
         <v>92</v>
       </c>
@@ -5385,7 +5515,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="12" t="s">
         <v>96</v>
       </c>
@@ -5399,7 +5532,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>99</v>
       </c>
@@ -5413,7 +5549,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>128</v>
       </c>
@@ -5427,7 +5566,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="12" t="s">
         <v>125</v>
       </c>
@@ -5441,7 +5583,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="12" t="s">
         <v>102</v>
       </c>
@@ -5455,7 +5600,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="39" t="s">
         <v>129</v>
       </c>
@@ -5469,7 +5617,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>111</v>
       </c>
@@ -5483,7 +5634,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="23" t="s">
         <v>130</v>
       </c>
@@ -5497,7 +5651,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="23" t="s">
         <v>133</v>
       </c>
@@ -5728,21 +5885,31 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60ED6AB-7469-4698-A695-2E8BCBEAD83F}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5756,7 +5923,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -5770,7 +5942,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>90</v>
       </c>
@@ -5784,7 +5965,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="G5" s="12" t="s">
         <v>109</v>
       </c>
@@ -5798,7 +5988,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="12" t="s">
         <v>125</v>
       </c>
@@ -5812,7 +6005,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="13" t="s">
         <v>145</v>
       </c>
@@ -5826,7 +6022,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="12" t="s">
         <v>102</v>
       </c>
@@ -5840,7 +6039,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>130</v>
       </c>
@@ -5854,7 +6056,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>119</v>
       </c>
@@ -5868,7 +6073,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="24" t="s">
         <v>128</v>
       </c>
@@ -5882,7 +6090,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="24" t="s">
         <v>134</v>
       </c>
@@ -5896,7 +6107,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="24" t="s">
         <v>99</v>
       </c>
@@ -5910,7 +6124,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="15" t="s">
         <v>92</v>
       </c>
@@ -5924,7 +6141,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="K15" s="14" t="s">
@@ -5934,7 +6154,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="K16" s="14" t="s">
@@ -6093,21 +6316,31 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF93BD0-8221-4F04-B861-3D32DC9024E1}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6121,7 +6354,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6135,7 +6373,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
@@ -6149,7 +6396,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>88</v>
       </c>
@@ -6163,7 +6419,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
       </c>
@@ -6177,7 +6436,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="14" t="s">
         <v>92</v>
       </c>
@@ -6191,7 +6453,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="14" t="s">
         <v>133</v>
       </c>
@@ -6205,7 +6470,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="14" t="s">
         <v>132</v>
       </c>
@@ -6219,7 +6487,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="14" t="s">
         <v>96</v>
       </c>
@@ -6233,7 +6504,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="14" t="s">
         <v>94</v>
       </c>
@@ -6247,7 +6521,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="14" t="s">
         <v>102</v>
       </c>
@@ -6261,7 +6538,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="23" t="s">
         <v>146</v>
       </c>
@@ -6275,7 +6555,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="23" t="s">
         <v>119</v>
       </c>
@@ -6289,7 +6572,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="23" t="s">
         <v>111</v>
       </c>
@@ -6303,7 +6589,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="23" t="s">
         <v>125</v>
       </c>
@@ -6570,21 +6859,31 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3796EF8C-0DF4-42C0-8E88-79C463DF95B7}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6598,7 +6897,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6612,7 +6916,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
@@ -6626,7 +6939,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>206</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>88</v>
       </c>
@@ -6640,7 +6962,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
       </c>
@@ -6654,7 +6979,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="24" t="s">
         <v>92</v>
       </c>
@@ -6668,7 +6996,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="24" t="s">
         <v>96</v>
       </c>
@@ -6682,7 +7013,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="24" t="s">
         <v>127</v>
       </c>
@@ -6696,7 +7030,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="24" t="s">
         <v>134</v>
       </c>
@@ -6710,7 +7047,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="38" t="s">
         <v>104</v>
       </c>
@@ -6724,7 +7064,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="25" t="s">
         <v>146</v>
       </c>
@@ -6738,7 +7081,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="25" t="s">
         <v>161</v>
       </c>
@@ -6752,7 +7098,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="25" t="s">
         <v>119</v>
       </c>
@@ -6766,7 +7115,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
@@ -6780,7 +7132,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="25" t="s">
         <v>164</v>
       </c>
@@ -7023,21 +7378,31 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C99364C-16DE-4EA8-AD87-2D8BFC5C34F4}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7051,7 +7416,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7065,7 +7435,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>88</v>
       </c>
@@ -7079,7 +7458,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>204</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>90</v>
       </c>
@@ -7093,7 +7481,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="36" t="s">
         <v>175</v>
       </c>
@@ -7107,7 +7498,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="12" t="s">
         <v>163</v>
       </c>
@@ -7121,7 +7515,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="13" t="s">
         <v>174</v>
       </c>
@@ -7135,7 +7532,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>165</v>
       </c>
@@ -7149,7 +7549,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>146</v>
       </c>
@@ -7163,7 +7566,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="12" t="s">
         <v>147</v>
       </c>
@@ -7177,7 +7583,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="12" t="s">
         <v>164</v>
       </c>
@@ -7191,7 +7600,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="34" t="s">
         <v>132</v>
       </c>
@@ -7205,7 +7617,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>177</v>
       </c>
@@ -7219,7 +7634,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="14" t="s">
         <v>178</v>
       </c>
@@ -7233,7 +7651,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="14" t="s">
         <v>141</v>
       </c>
@@ -7488,21 +7909,31 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E99AFAD-4CB3-492B-BAFB-AA98FB2D25D5}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7516,7 +7947,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7530,7 +7966,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
@@ -7544,7 +7989,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>209</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>88</v>
       </c>
@@ -7558,7 +8012,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
       </c>
@@ -7572,7 +8029,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="20"/>
       <c r="G7" s="23" t="s">
         <v>92</v>
       </c>
@@ -7586,7 +8046,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="20"/>
       <c r="G8" s="23" t="s">
         <v>165</v>
       </c>
@@ -7600,7 +8063,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="20"/>
       <c r="G9" s="16" t="s">
         <v>190</v>
       </c>
@@ -7614,7 +8080,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="20"/>
       <c r="G10" s="23" t="s">
         <v>114</v>
       </c>
@@ -7628,7 +8097,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="20"/>
       <c r="G11" s="16" t="s">
         <v>191</v>
       </c>
@@ -7642,7 +8114,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="20"/>
       <c r="G12" s="14" t="s">
         <v>177</v>
       </c>
@@ -7656,7 +8131,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="20"/>
       <c r="G13" s="14" t="s">
         <v>178</v>
       </c>
@@ -7670,7 +8148,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>141</v>
       </c>
@@ -7684,7 +8165,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="20"/>
       <c r="G15" s="39" t="s">
         <v>192</v>
       </c>
@@ -7698,7 +8182,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="20"/>
       <c r="G16" s="39" t="s">
         <v>194</v>
       </c>
@@ -7933,6 +8420,10 @@
       <c r="L42" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
+++ b/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4780AB0-D514-48BF-B10B-41CFC43C0E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138D7F41-528C-4FFC-9076-4AF12B792ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
   </bookViews>
   <sheets>
     <sheet name="Barbarossa" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="211">
   <si>
     <t>Scenario</t>
   </si>
@@ -4163,12 +4163,54 @@
     <t>No Carvel Hull
 No Spies</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Murder Holes and Herbal Medicine automatically researched for Teutons
+War Galley and Fervor are researched automatically
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Moderate /Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: Sanctity is researched automatically
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Redemption is researched automatically</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4401,6 +4443,12 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4712,6 +4760,15 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4728,15 +4785,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5398,11 +5446,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5417,11 +5465,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="9" t="s">
         <v>83</v>
       </c>
@@ -5459,13 +5507,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>207</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -5482,8 +5530,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
@@ -5499,8 +5547,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="12" t="s">
         <v>92</v>
@@ -5516,8 +5564,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="12" t="s">
         <v>96</v>
@@ -5533,8 +5581,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>99</v>
@@ -5550,8 +5598,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>128</v>
@@ -5567,8 +5615,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="12" t="s">
         <v>125</v>
@@ -5584,8 +5632,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="12" t="s">
         <v>102</v>
@@ -5601,8 +5649,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="39" t="s">
         <v>129</v>
@@ -5618,8 +5666,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>111</v>
@@ -5635,8 +5683,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="23" t="s">
         <v>130</v>
@@ -5652,8 +5700,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="23" t="s">
         <v>133</v>
@@ -5905,11 +5953,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5924,11 +5972,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -5966,13 +6014,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>207</v>
       </c>
       <c r="G5" s="12" t="s">
@@ -5989,8 +6037,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="12" t="s">
         <v>125</v>
@@ -6006,8 +6054,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="13" t="s">
         <v>145</v>
@@ -6023,8 +6071,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="12" t="s">
         <v>102</v>
@@ -6040,8 +6088,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>130</v>
@@ -6057,8 +6105,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>119</v>
@@ -6074,8 +6122,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="24" t="s">
         <v>128</v>
@@ -6091,8 +6139,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="24" t="s">
         <v>134</v>
@@ -6108,8 +6156,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="24" t="s">
         <v>99</v>
@@ -6125,8 +6173,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="15" t="s">
         <v>92</v>
@@ -6142,8 +6190,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
@@ -6155,8 +6203,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
@@ -6336,11 +6384,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6355,11 +6403,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6396,15 +6444,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+    <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>207</v>
+      <c r="D5" s="46" t="s">
+        <v>210</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>88</v>
@@ -6420,8 +6468,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
@@ -6437,8 +6485,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="14" t="s">
         <v>92</v>
@@ -6454,8 +6502,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="14" t="s">
         <v>133</v>
@@ -6471,8 +6519,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="14" t="s">
         <v>132</v>
@@ -6488,8 +6536,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="14" t="s">
         <v>96</v>
@@ -6505,8 +6553,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="14" t="s">
         <v>94</v>
@@ -6522,8 +6570,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="14" t="s">
         <v>102</v>
@@ -6539,8 +6587,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="23" t="s">
         <v>146</v>
@@ -6556,8 +6604,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="23" t="s">
         <v>119</v>
@@ -6573,8 +6621,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="23" t="s">
         <v>111</v>
@@ -6590,8 +6638,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="23" t="s">
         <v>125</v>
@@ -6864,6 +6912,7 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6879,11 +6928,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6898,11 +6947,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6940,13 +6989,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>206</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -6963,8 +7012,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
@@ -6980,8 +7029,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="24" t="s">
         <v>92</v>
@@ -6997,8 +7046,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="24" t="s">
         <v>96</v>
@@ -7014,8 +7063,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="24" t="s">
         <v>127</v>
@@ -7031,8 +7080,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="24" t="s">
         <v>134</v>
@@ -7048,8 +7097,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="38" t="s">
         <v>104</v>
@@ -7065,8 +7114,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="25" t="s">
         <v>146</v>
@@ -7082,8 +7131,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="25" t="s">
         <v>161</v>
@@ -7099,8 +7148,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="25" t="s">
         <v>119</v>
@@ -7116,8 +7165,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="25" t="s">
         <v>121</v>
@@ -7133,8 +7182,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="25" t="s">
         <v>164</v>
@@ -7398,11 +7447,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7417,11 +7466,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7459,13 +7508,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>204</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -7482,8 +7531,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="36" t="s">
         <v>175</v>
@@ -7499,8 +7548,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="12" t="s">
         <v>163</v>
@@ -7516,8 +7565,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="13" t="s">
         <v>174</v>
@@ -7533,8 +7582,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="12" t="s">
         <v>165</v>
@@ -7550,8 +7599,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="12" t="s">
         <v>146</v>
@@ -7567,8 +7616,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="12" t="s">
         <v>147</v>
@@ -7584,8 +7633,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="12" t="s">
         <v>164</v>
@@ -7601,8 +7650,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="34" t="s">
         <v>132</v>
@@ -7618,8 +7667,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>177</v>
@@ -7635,8 +7684,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="14" t="s">
         <v>178</v>
@@ -7652,8 +7701,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="14" t="s">
         <v>141</v>
@@ -7929,11 +7978,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7948,11 +7997,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7990,13 +8039,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="46" t="s">
         <v>209</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -8013,8 +8062,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="G6" s="9" t="s">
         <v>90</v>
@@ -8030,8 +8079,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="G7" s="23" t="s">
         <v>92</v>
@@ -8047,8 +8096,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20"/>
       <c r="G8" s="23" t="s">
         <v>165</v>
@@ -8064,8 +8113,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="G9" s="16" t="s">
         <v>190</v>
@@ -8081,8 +8130,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
       <c r="D10" s="20"/>
       <c r="G10" s="23" t="s">
         <v>114</v>
@@ -8098,8 +8147,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20"/>
       <c r="G11" s="16" t="s">
         <v>191</v>
@@ -8115,8 +8164,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="G12" s="14" t="s">
         <v>177</v>
@@ -8132,8 +8181,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="G13" s="14" t="s">
         <v>178</v>
@@ -8149,8 +8198,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="20"/>
       <c r="G14" s="14" t="s">
         <v>141</v>
@@ -8166,8 +8215,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
       <c r="D15" s="20"/>
       <c r="G15" s="39" t="s">
         <v>192</v>
@@ -8183,8 +8232,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
       <c r="D16" s="20"/>
       <c r="G16" s="39" t="s">
         <v>194</v>

--- a/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
+++ b/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138D7F41-528C-4FFC-9076-4AF12B792ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF8E339-91C0-42BE-97F1-B050B3BAF2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
   </bookViews>
   <sheets>
     <sheet name="Barbarossa" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="217">
   <si>
     <t>Scenario</t>
   </si>
@@ -4204,6 +4204,24 @@
       </rPr>
       <t>: Redemption is researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Elite Teutonic Knight</t>
+  </si>
+  <si>
+    <t>Emperor in a Barrel</t>
   </si>
 </sst>
 </file>
@@ -4461,7 +4479,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -4621,11 +4639,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4766,9 +4819,6 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4785,6 +4835,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5439,18 +5507,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5465,11 +5533,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="9" t="s">
         <v>83</v>
       </c>
@@ -5546,7 +5614,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -5563,10 +5631,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="12" t="s">
         <v>96</v>
       </c>
@@ -5581,9 +5658,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="56"/>
       <c r="G9" s="12" t="s">
         <v>99</v>
       </c>
@@ -5598,9 +5682,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="56"/>
       <c r="G10" s="12" t="s">
         <v>128</v>
       </c>
@@ -5615,9 +5706,16 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="56"/>
       <c r="G11" s="12" t="s">
         <v>125</v>
       </c>
@@ -5632,9 +5730,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
       <c r="G12" s="12" t="s">
         <v>102</v>
       </c>
@@ -5649,9 +5750,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="G13" s="39" t="s">
         <v>129</v>
       </c>
@@ -5666,9 +5770,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="G14" s="14" t="s">
         <v>111</v>
       </c>
@@ -5683,9 +5788,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="G15" s="23" t="s">
         <v>130</v>
       </c>
@@ -5700,9 +5806,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="G16" s="23" t="s">
         <v>133</v>
       </c>
@@ -5716,7 +5823,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="G17" s="23" t="s">
         <v>94</v>
       </c>
@@ -5730,7 +5841,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="23" t="s">
         <v>134</v>
       </c>
@@ -5744,7 +5859,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="38" t="s">
         <v>131</v>
       </c>
@@ -5758,7 +5877,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="24" t="s">
         <v>132</v>
       </c>
@@ -5772,7 +5895,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="25" t="s">
         <v>136</v>
       </c>
@@ -5786,7 +5913,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="40" t="s">
         <v>137</v>
       </c>
@@ -5800,7 +5927,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25" t="s">
         <v>124</v>
       </c>
@@ -5814,7 +5941,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25" t="s">
         <v>138</v>
       </c>
@@ -5824,7 +5951,7 @@
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="41" t="s">
         <v>139</v>
       </c>
@@ -5834,7 +5961,7 @@
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="41" t="s">
         <v>140</v>
       </c>
@@ -5844,7 +5971,7 @@
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="26" t="s">
         <v>141</v>
       </c>
@@ -5854,31 +5981,31 @@
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="K32" s="27"/>
@@ -5947,17 +6074,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -5972,11 +6100,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6053,7 +6181,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -6070,10 +6198,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="12" t="s">
         <v>102</v>
       </c>
@@ -6088,9 +6225,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="56"/>
       <c r="G9" s="12" t="s">
         <v>130</v>
       </c>
@@ -6105,9 +6249,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="12" t="s">
         <v>119</v>
       </c>
@@ -6122,9 +6271,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
       <c r="G11" s="24" t="s">
         <v>128</v>
       </c>
@@ -6139,9 +6293,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
       <c r="G12" s="24" t="s">
         <v>134</v>
       </c>
@@ -6156,9 +6315,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="G13" s="24" t="s">
         <v>99</v>
       </c>
@@ -6173,9 +6335,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="G14" s="15" t="s">
         <v>92</v>
       </c>
@@ -6190,9 +6355,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="K15" s="14" t="s">
@@ -6203,9 +6371,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="K16" s="14" t="s">
@@ -6215,7 +6386,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="K17" s="15" t="s">
@@ -6225,91 +6400,107 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="27"/>
       <c r="H18" s="27"/>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
       <c r="K19" s="27"/>
       <c r="L19" s="27"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="27"/>
       <c r="H20" s="27"/>
       <c r="K20" s="27"/>
       <c r="L20" s="27"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
       <c r="K21" s="27"/>
       <c r="L21" s="27"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="K22" s="27"/>
       <c r="L22" s="27"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="27"/>
       <c r="H23" s="27"/>
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="27"/>
       <c r="H24" s="27"/>
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="27"/>
       <c r="H25" s="27"/>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="K32" s="27"/>
@@ -6378,17 +6569,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6403,11 +6595,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -6484,7 +6676,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -6501,10 +6693,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="14" t="s">
         <v>133</v>
       </c>
@@ -6519,9 +6720,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
       <c r="G9" s="14" t="s">
         <v>132</v>
       </c>
@@ -6536,9 +6742,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="14" t="s">
         <v>96</v>
       </c>
@@ -6553,9 +6764,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
       <c r="G11" s="14" t="s">
         <v>94</v>
       </c>
@@ -6570,9 +6786,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
       <c r="G12" s="14" t="s">
         <v>102</v>
       </c>
@@ -6587,9 +6806,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="G13" s="23" t="s">
         <v>146</v>
       </c>
@@ -6604,9 +6826,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="G14" s="23" t="s">
         <v>119</v>
       </c>
@@ -6621,9 +6846,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="G15" s="23" t="s">
         <v>111</v>
       </c>
@@ -6638,9 +6864,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="G16" s="23" t="s">
         <v>125</v>
       </c>
@@ -6654,7 +6881,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="G17" s="23" t="s">
         <v>134</v>
       </c>
@@ -6668,7 +6899,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="23" t="s">
         <v>147</v>
       </c>
@@ -6682,7 +6917,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="25" t="s">
         <v>126</v>
       </c>
@@ -6696,7 +6935,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="25" t="s">
         <v>127</v>
       </c>
@@ -6710,7 +6953,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="25" t="s">
         <v>121</v>
       </c>
@@ -6724,7 +6971,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="40" t="s">
         <v>149</v>
       </c>
@@ -6738,7 +6985,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="25" t="s">
         <v>150</v>
       </c>
@@ -6752,7 +6999,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
       <c r="G24" s="40" t="s">
         <v>151</v>
       </c>
@@ -6766,7 +7013,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="40" t="s">
         <v>152</v>
       </c>
@@ -6776,7 +7023,7 @@
       <c r="K25" s="19"/>
       <c r="L25" s="19"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="25" t="s">
         <v>153</v>
       </c>
@@ -6786,7 +7033,7 @@
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="12" t="s">
         <v>99</v>
       </c>
@@ -6796,7 +7043,7 @@
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="12" t="s">
         <v>109</v>
       </c>
@@ -6806,7 +7053,7 @@
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="13" t="s">
         <v>154</v>
       </c>
@@ -6816,7 +7063,7 @@
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
     </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G30" s="12" t="s">
         <v>155</v>
       </c>
@@ -6826,7 +7073,7 @@
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="12" t="s">
         <v>156</v>
       </c>
@@ -6836,7 +7083,7 @@
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="12" t="s">
         <v>130</v>
       </c>
@@ -6922,17 +7169,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6947,11 +7195,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7028,7 +7276,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -7045,10 +7293,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="24" t="s">
         <v>96</v>
       </c>
@@ -7063,9 +7320,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="56"/>
       <c r="G9" s="24" t="s">
         <v>127</v>
       </c>
@@ -7080,9 +7344,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="56"/>
       <c r="G10" s="24" t="s">
         <v>134</v>
       </c>
@@ -7097,9 +7368,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="56"/>
       <c r="G11" s="38" t="s">
         <v>104</v>
       </c>
@@ -7114,9 +7390,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="56"/>
       <c r="G12" s="25" t="s">
         <v>146</v>
       </c>
@@ -7131,9 +7412,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="56"/>
       <c r="G13" s="25" t="s">
         <v>161</v>
       </c>
@@ -7148,9 +7434,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="G14" s="25" t="s">
         <v>119</v>
       </c>
@@ -7165,9 +7452,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="G15" s="25" t="s">
         <v>121</v>
       </c>
@@ -7182,9 +7470,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="G16" s="25" t="s">
         <v>164</v>
       </c>
@@ -7198,7 +7487,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="G17" s="25" t="s">
         <v>163</v>
       </c>
@@ -7212,7 +7505,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="25" t="s">
         <v>153</v>
       </c>
@@ -7226,7 +7523,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="14" t="s">
         <v>94</v>
       </c>
@@ -7240,7 +7541,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="14" t="s">
         <v>155</v>
       </c>
@@ -7254,7 +7559,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="14" t="s">
         <v>136</v>
       </c>
@@ -7268,7 +7577,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>165</v>
       </c>
@@ -7282,7 +7591,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>114</v>
       </c>
@@ -7296,7 +7605,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="14" t="s">
         <v>157</v>
       </c>
@@ -7306,7 +7615,7 @@
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="9" t="s">
         <v>166</v>
       </c>
@@ -7316,7 +7625,7 @@
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="16" t="s">
         <v>167</v>
       </c>
@@ -7326,7 +7635,7 @@
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="23" t="s">
         <v>99</v>
       </c>
@@ -7336,7 +7645,7 @@
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23" t="s">
         <v>156</v>
       </c>
@@ -7346,7 +7655,7 @@
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G29" s="9" t="s">
         <v>168</v>
       </c>
@@ -7356,7 +7665,7 @@
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
     </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G30" s="31" t="s">
         <v>199</v>
       </c>
@@ -7366,13 +7675,13 @@
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="K32" s="27"/>
@@ -7441,17 +7750,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7466,11 +7776,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -7547,7 +7857,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -7564,10 +7874,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="13" t="s">
         <v>174</v>
       </c>
@@ -7582,9 +7901,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>101</v>
+      </c>
       <c r="G9" s="12" t="s">
         <v>165</v>
       </c>
@@ -7599,9 +7925,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="56"/>
       <c r="G10" s="12" t="s">
         <v>146</v>
       </c>
@@ -7616,9 +7947,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="56"/>
       <c r="G11" s="12" t="s">
         <v>147</v>
       </c>
@@ -7633,9 +7969,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12" s="56"/>
       <c r="G12" s="12" t="s">
         <v>164</v>
       </c>
@@ -7649,10 +7990,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="56"/>
       <c r="G13" s="34" t="s">
         <v>132</v>
       </c>
@@ -7667,9 +8013,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="56"/>
       <c r="G14" s="14" t="s">
         <v>177</v>
       </c>
@@ -7684,9 +8035,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="56"/>
+      <c r="D15" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="56"/>
       <c r="G15" s="14" t="s">
         <v>178</v>
       </c>
@@ -7700,10 +8056,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="56"/>
       <c r="G16" s="14" t="s">
         <v>141</v>
       </c>
@@ -7717,7 +8078,13 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="56"/>
       <c r="G17" s="14" t="s">
         <v>121</v>
       </c>
@@ -7731,7 +8098,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="14" t="s">
         <v>161</v>
       </c>
@@ -7745,7 +8116,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="14" t="s">
         <v>150</v>
       </c>
@@ -7759,7 +8134,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="39" t="s">
         <v>180</v>
       </c>
@@ -7773,7 +8152,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="23" t="s">
         <v>182</v>
       </c>
@@ -7787,7 +8170,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="23" t="s">
         <v>99</v>
       </c>
@@ -7801,7 +8184,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="23" t="s">
         <v>153</v>
       </c>
@@ -7815,7 +8198,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="23" t="s">
         <v>114</v>
       </c>
@@ -7829,7 +8212,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="24" t="s">
         <v>94</v>
       </c>
@@ -7843,7 +8226,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="24" t="s">
         <v>134</v>
       </c>
@@ -7857,7 +8240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="24" t="s">
         <v>136</v>
       </c>
@@ -7871,7 +8254,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G28" s="42" t="s">
         <v>184</v>
       </c>
@@ -7885,25 +8268,25 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="K29" s="19"/>
       <c r="L29" s="19"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="K32" s="27"/>
@@ -7972,17 +8355,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
       <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
@@ -7997,11 +8381,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="G3" s="11" t="s">
         <v>83</v>
       </c>
@@ -8078,7 +8462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="47"/>
       <c r="C7" s="47"/>
       <c r="D7" s="20"/>
@@ -8095,10 +8479,19 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="20"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="G8" s="23" t="s">
         <v>165</v>
       </c>
@@ -8113,9 +8506,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
       <c r="G9" s="16" t="s">
         <v>190</v>
       </c>
@@ -8130,9 +8528,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="23" t="s">
         <v>114</v>
       </c>
@@ -8147,9 +8548,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="20"/>
+      <c r="B11" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
       <c r="G11" s="16" t="s">
         <v>191</v>
       </c>
@@ -8164,9 +8568,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
       <c r="G12" s="14" t="s">
         <v>177</v>
       </c>
@@ -8180,10 +8587,13 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="20"/>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="G13" s="14" t="s">
         <v>178</v>
       </c>
@@ -8198,9 +8608,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="G14" s="14" t="s">
         <v>141</v>
       </c>
@@ -8215,9 +8626,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="G15" s="39" t="s">
         <v>192</v>
       </c>
@@ -8232,9 +8644,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
       <c r="G16" s="39" t="s">
         <v>194</v>
       </c>
@@ -8248,7 +8661,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="G17" s="14" t="s">
         <v>182</v>
       </c>
@@ -8262,7 +8679,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="G18" s="14" t="s">
         <v>123</v>
       </c>
@@ -8276,7 +8697,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
       <c r="G19" s="14" t="s">
         <v>99</v>
       </c>
@@ -8290,7 +8715,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
       <c r="G20" s="12" t="s">
         <v>163</v>
       </c>
@@ -8304,7 +8733,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="G21" s="12" t="s">
         <v>124</v>
       </c>
@@ -8318,7 +8751,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="24" t="s">
         <v>136</v>
       </c>
@@ -8332,7 +8765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="38" t="s">
         <v>195</v>
       </c>
@@ -8346,7 +8779,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
         <v>196</v>
       </c>
@@ -8360,7 +8793,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="42" t="s">
         <v>197</v>
       </c>
@@ -8374,7 +8807,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="K26" s="44" t="s">
@@ -8384,37 +8817,37 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="K27" s="19"/>
       <c r="L27" s="19"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="K31" s="27"/>
       <c r="L31" s="27"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="K32" s="27"/>
